--- a/rules.xlsx
+++ b/rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{D9BDF1D3-F3B6-3546-BEBF-DBE8B0765AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E7C78B0-DAFC-844B-9EDD-7BF62CAA4CC3}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{D9BDF1D3-F3B6-3546-BEBF-DBE8B0765AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C356E05-7590-3D4E-A92D-C9E5703F7EF7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
+    <workbookView xWindow="9600" yWindow="3000" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Value</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>Set to 0 if first weekend is A, 1 if B</t>
+  </si>
+  <si>
+    <t>vac</t>
+  </si>
+  <si>
+    <t>nc</t>
+  </si>
+  <si>
+    <t>Number of hours credited toward a day of vacation</t>
+  </si>
+  <si>
+    <t>Number of hours credited for a non-clinical workday</t>
   </si>
 </sst>
 </file>
@@ -108,7 +120,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,6 +136,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -155,16 +173,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5726D70-3220-EE45-8CC4-80523B43DD04}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
@@ -522,7 +543,9 @@
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
@@ -531,7 +554,9 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
@@ -540,7 +565,9 @@
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
@@ -549,7 +576,9 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="4">
+        <v>2</v>
+      </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
@@ -558,7 +587,9 @@
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="4">
+        <v>30</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
@@ -567,7 +598,9 @@
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
@@ -576,7 +609,9 @@
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="4">
+        <v>10</v>
+      </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
@@ -585,9 +620,33 @@
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="4">
+        <v>7</v>
+      </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="4">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/rules.xlsx
+++ b/rules.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{D9BDF1D3-F3B6-3546-BEBF-DBE8B0765AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C356E05-7590-3D4E-A92D-C9E5703F7EF7}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="13_ncr:1_{D9BDF1D3-F3B6-3546-BEBF-DBE8B0765AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B720390-D1BA-CA43-AB09-13451BB472A6}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="3000" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
+    <workbookView xWindow="-28800" yWindow="6840" windowWidth="28800" windowHeight="17500" xr2:uid="{F6C4B857-2221-7442-B2F7-99991C74024F}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -59,18 +59,9 @@
     <t>first_monday</t>
   </si>
   <si>
-    <t>max_per_n</t>
-  </si>
-  <si>
-    <t>min_post_n</t>
-  </si>
-  <si>
     <t>Minimum number of days between the beginning of two nightshift periods</t>
   </si>
   <si>
-    <t>min_betw_n</t>
-  </si>
-  <si>
     <t>first_weekend</t>
   </si>
   <si>
@@ -95,16 +86,25 @@
     <t>Set to 0 if first weekend is A, 1 if B</t>
   </si>
   <si>
-    <t>vac</t>
-  </si>
-  <si>
-    <t>nc</t>
-  </si>
-  <si>
     <t>Number of hours credited toward a day of vacation</t>
   </si>
   <si>
     <t>Number of hours credited for a non-clinical workday</t>
+  </si>
+  <si>
+    <t>alpha_vac</t>
+  </si>
+  <si>
+    <t>alpha_nc</t>
+  </si>
+  <si>
+    <t>B_n</t>
+  </si>
+  <si>
+    <t>L_n</t>
+  </si>
+  <si>
+    <t>Dist_n</t>
   </si>
 </sst>
 </file>
@@ -202,6 +202,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,18 +556,18 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B4" s="4">
         <v>2</v>
@@ -574,7 +578,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4">
         <v>2</v>
@@ -585,68 +589,68 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4">
         <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4">
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="4">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
